--- a/imagenes_nautica_adicionales 3.xlsx
+++ b/imagenes_nautica_adicionales 3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Estudios y certificaciones\ESTUDIOS DE PROGRAMMING\PROGRAMMING\PERSONAL\PYTHON\Image_Generator_API\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{120F45A8-51E9-43D7-BE09-EBA1DED1EAE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA6F368F-33FD-4160-8B02-88652F53970B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{4B59B5B9-E1CB-493C-A8AC-297F4A866392}"/>
   </bookViews>
@@ -108,67 +108,6 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>28575</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>742950</xdr:colOff>
-      <xdr:row>55</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Imagen 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{83AFD2E3-7461-3D4C-3657-3AD0761F3081}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="2314575" y="5743575"/>
-          <a:ext cx="6810375" cy="4886325"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
       <xdr:colOff>19050</xdr:colOff>
       <xdr:row>58</xdr:row>
       <xdr:rowOff>19050</xdr:rowOff>
@@ -193,7 +132,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -254,7 +193,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -315,7 +254,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -376,7 +315,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -732,12 +671,9 @@
         <v>208004741</v>
       </c>
     </row>
-    <row r="31" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B31">
         <v>2</v>
-      </c>
-      <c r="C31">
-        <v>208004397</v>
       </c>
     </row>
     <row r="59" spans="2:3" x14ac:dyDescent="0.25">
